--- a/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_word_repeat_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_raw_table_typo-test-09-30.xlsx
+++ b/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_word_repeat_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_raw_table_typo-test-09-30.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What is the the location location location of Eibenstock?</t>
+          <t>What What is the location location of of Eibenstock?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,19 +509,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>What is the the location location location of Eibenstock? Answer: Eibenstock is located in the state of Saxony, Germany. The latitude of Eibenstock is 50.45</t>
+          <t>What What is the location location of of Eibenstock? Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany. The town is</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is located in the state of Saxony, Germany</t>
+          <t>Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>0.5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9480774998664856</v>
+        <v>0.9675318002700806</v>
       </c>
       <c r="I2" t="n">
         <v>0.3465735912322998</v>
@@ -531,7 +531,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' state', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (',', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 0.5), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What is the the location location location of Eibenstock?</t>
+          <t>What What is the location location of of Eibenstock?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -557,19 +557,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>What is the the location location location of Eibenstock? Answer: Eibenstock is located in the state of Saxony, Germany. The latitude of Eibenstock is 50.466</t>
+          <t>What What is the location location of of Eibenstock? Answer: Eibenstock is located in the district of Erzgebirgskreis in the state of Saxony in Germany</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is located in the state of Saxony, Germany</t>
+          <t>Answer: Eibenstock is located in the district of Erzgebirgskreis in the state of Saxony in Germany</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9480774998664856</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I3" t="n">
         <v>0.3465735912322998</v>
@@ -579,7 +579,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' state', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (',', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Er', 0.5), ('z', 1.0), ('geb', 1.0), ('ir', 1.0), ('g', 1.0), ('sk', 1.0), ('re', 1.0), ('is', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -592,7 +592,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What is the the location location location of Eibenstock?</t>
+          <t>What What is the location location of of Eibenstock?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -605,19 +605,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>What is the the location location location of Eibenstock? Answer: Eibenstock is located in the state of Saxony, Germany. The latitude of Eibenstock is 50.466</t>
+          <t>What What is the location location of of Eibenstock? Answer: Eibenstock is located in the district of Erzgebirgskreis in the state of Saxony in Germany</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is located in the state of Saxony, Germany</t>
+          <t>Answer: Eibenstock is located in the district of Erzgebirgskreis in the state of Saxony in Germany</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9480774998664856</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I4" t="n">
         <v>0.3465735912322998</v>
@@ -627,7 +627,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' state', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (',', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Er', 0.5), ('z', 1.0), ('geb', 1.0), ('ir', 1.0), ('g', 1.0), ('sk', 1.0), ('re', 1.0), ('is', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What is the the location location location of Eibenstock?</t>
+          <t>What What is the location location of of Eibenstock?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -653,19 +653,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>What is the the location location location of Eibenstock? Answer: Eibenstock is located in the state of Saxony, Germany. The latitude of Eibenstock is 50.466</t>
+          <t>What What is the location location of of Eibenstock? Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany. The town is</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is located in the state of Saxony, Germany</t>
+          <t>Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0.5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9480774998664856</v>
+        <v>0.9675318002700806</v>
       </c>
       <c r="I5" t="n">
         <v>0.3465735912322998</v>
@@ -675,7 +675,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' state', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (',', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 0.5), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What is the the location location location of Eibenstock?</t>
+          <t>What What is the location location of of Eibenstock?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -701,19 +701,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>What is the the location location location of Eibenstock? Answer: Eibenstock is located in Germany (Sachsen) and the time zone is Europe/Berlin. It has an elevation</t>
+          <t>What What is the location location of of Eibenstock? Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany. The town is</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is located in Germany (Sachsen) and the time zone is Europe/Berlin</t>
+          <t>Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9057236313819885</v>
+        <v>0.9675318002700806</v>
       </c>
       <c r="I6" t="n">
         <v>0.3465735912322998</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Germany', 0.5)]</t>
+          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 0.5), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -736,7 +736,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What is the the location location of Simcoe Simcoe Composite School?</t>
+          <t>What is is the location location of Simcoe Composite Composite School?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -749,31 +749,31 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>What is the the location location of Simcoe Simcoe Composite School? Answer: Simcoe Composite School is located at 1 Maple Ave Simcoe, ON N3Y 4G8.
-What is</t>
+          <t xml:space="preserve">What is is the location location of Simcoe Composite Composite School? Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3.
+</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1 Maple Ave Simcoe, ON N3Y 4G8.
-What is</t>
+          <t xml:space="preserve">Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3.
+</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.01403080485761166</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8431081771850586</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I7" t="n">
-        <v>0.944916844367981</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Maple', 0.1821), (' Ave', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' ON', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('G', 0.5), ('8', 0.1541), ('.\n', 1.0), ('What', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), ('.\n', 0.6514)]</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What is the the location location of Simcoe Simcoe Composite School?</t>
+          <t>What is is the location location of Simcoe Composite Composite School?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -799,31 +799,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>What is the the location location of Simcoe Simcoe Composite School? Answer: Simcoe Composite School is located at 1 Maple Ave Simcoe, ON N3Y 4G3.
-What is</t>
+          <t>What is is the location location of Simcoe Composite Composite School? Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1 Maple Ave Simcoe, ON N3Y 4G3.
-What is</t>
+          <t>Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3.</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.04896668344736099</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8863312005996704</v>
+        <v>0.9587228894233704</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9903066158294678</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Maple', 0.1821), (' Ave', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' ON', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('G', 0.5), ('3', 0.5378), ('.\n', 1.0), ('What', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), ('.', 0.3486)]</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -836,7 +834,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What is the the location location of Simcoe Simcoe Composite School?</t>
+          <t>What is is the location location of Simcoe Composite Composite School?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -849,29 +847,31 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>What is the the location location of Simcoe Simcoe Composite School? Answer: Simcoe Composite School is located at 1 1st Ave, Simcoe, ON N3Y 4H3</t>
+          <t xml:space="preserve">What is is the location location of Simcoe Composite Composite School? Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3.
+</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1 1st Ave, Simcoe, ON N3Y 4H3</t>
+          <t xml:space="preserve">Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3.
+</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.1820999979972839</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9341409206390381</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3101525902748108</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' ', 0.1821), ('1', 1.0), ('st', 1.0), (' Ave', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' ON', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), ('.\n', 0.6514)]</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -884,7 +884,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What is the the location location of Simcoe Simcoe Composite School?</t>
+          <t>What is is the location location of Simcoe Composite Composite School?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -897,29 +897,31 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>What is the the location location of Simcoe Simcoe Composite School? Answer: Simcoe Composite School is located at 1 Simcoe St, Simcoe, ON N3Y 4H3,</t>
+          <t xml:space="preserve">What is is the location location of Simcoe Composite Composite School? Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3.
+</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1 Simcoe St, Simcoe, ON N3Y 4H3,</t>
+          <t xml:space="preserve">Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3.
+</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.635699987411499</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9820420742034912</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2879902422428131</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 0.6357), ('coe', 1.0), (' St', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' ON', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), (',', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), ('.\n', 0.6514)]</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -932,7 +934,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What is the the location location of Simcoe Simcoe Composite School?</t>
+          <t>What is is the location location of Simcoe Composite Composite School?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -945,29 +947,31 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>What is the the location location of Simcoe Simcoe Composite School? Answer: Simcoe Composite School is located at 1 1st Ave, Simcoe, ON N3Y 4H3</t>
+          <t xml:space="preserve">What is is the location location of Simcoe Composite Composite School? Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3.
+</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1 1st Ave, Simcoe, ON N3Y 4H3</t>
+          <t xml:space="preserve">Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3.
+</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.1820999979972839</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9341409206390381</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3101525902748108</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' ', 0.1821), ('1', 1.0), ('st', 1.0), (' Ave', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' ON', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), ('.\n', 0.6514)]</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -980,7 +984,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What is the location of of of Vrienden van van het Platteland?</t>
+          <t>What is is is the location location of Vrienden van het Platteland?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -993,33 +997,33 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>What is the location of of of Vrienden van van het Platteland? Answer: Vrienden van het Platteland is located at: 1, 1, 1, 1, 1</t>
+          <t xml:space="preserve">What is is is the location location of Vrienden van het Platteland? Answer: Vrienden van het Platteland is located in the Netherlands. Coordinates of Vrienden van het Platteland is: </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located at: 1, 1, 1, 1, 1</t>
+          <t>Answer: Vrienden van het Platteland is located in the Netherlands</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>[(' V', 0.5), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0)]</t>
+          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1028,7 +1032,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What is the location of of of Vrienden van van het Platteland?</t>
+          <t>What is is is the location location of Vrienden van het Platteland?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1041,33 +1045,33 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>What is the location of of of Vrienden van van het Platteland? Answer: The location of of of Vrienden van van het Platteland is: 51.2167° N, 3</t>
+          <t xml:space="preserve">What is is is the location location of Vrienden van het Platteland? Answer: Vrienden van het Platteland is located in the Netherlands. Coordinates of Vrienden van het Platteland is: </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Answer: The location of of of Vrienden van van het Platteland is: 51.2167° N, 3</t>
+          <t>Answer: Vrienden van het Platteland is located in the Netherlands</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.2214000076055527</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9414713382720947</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8007386922836304</v>
+        <v>-0</v>
       </c>
       <c r="J13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' location', 1.0), (' of', 1.0), (' of', 1.0), (' of', 1.0), (' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (':', 1.0), (' ', 1.0), ('51', 1.0), ('.', 1.0), ('216', 0.8856), ('7', 1.0), ('°', 1.0), (' N', 1.0), (',', 1.0), (' ', 1.0), ('3', 0.5)]</t>
+          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1076,7 +1080,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>What is the location of of of Vrienden van van het Platteland?</t>
+          <t>What is is is the location location of Vrienden van het Platteland?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1089,33 +1093,33 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>What is the location of of of Vrienden van van het Platteland? Answer: Vrienden van het Platteland is located at: 1, 1, 1, 1, 1</t>
+          <t xml:space="preserve">What is is is the location location of Vrienden van het Platteland? Answer: Vrienden van het Platteland is located in the Netherlands. Coordinates of Vrienden van het Platteland is: </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located at: 1, 1, 1, 1, 1</t>
+          <t>Answer: Vrienden van het Platteland is located in the Netherlands</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>[(' V', 0.5), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0)]</t>
+          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1124,7 +1128,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What is the location of of of Vrienden van van het Platteland?</t>
+          <t>What is is is the location location of Vrienden van het Platteland?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1137,33 +1141,33 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>What is the location of of of Vrienden van van het Platteland? Answer: Vrienden van het Platteland is located at: 1, 1, 1, 1, 1</t>
+          <t xml:space="preserve">What is is is the location location of Vrienden van het Platteland? Answer: Vrienden van het Platteland is located in the Netherlands. Coordinates of Vrienden van het Platteland is: </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located at: 1, 1, 1, 1, 1</t>
+          <t>Answer: Vrienden van het Platteland is located in the Netherlands</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>[(' V', 0.5), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0)]</t>
+          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1172,7 +1176,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>What is the location of of of Vrienden van van het Platteland?</t>
+          <t>What is is is the location location of Vrienden van het Platteland?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1185,33 +1189,33 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>What is the location of of of Vrienden van van het Platteland? Answer: Vrienden van het Platteland is located at: 1, 1, 1, 1, 1</t>
+          <t xml:space="preserve">What is is is the location location of Vrienden van het Platteland? Answer: Vrienden van het Platteland is located in the Netherlands. Coordinates of Vrienden van het Platteland is: </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located at: 1, 1, 1, 1, 1</t>
+          <t>Answer: Vrienden van het Platteland is located in the Netherlands</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>[(' V', 0.5), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0)]</t>
+          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1220,7 +1224,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What What is the the location of Cunter? Cunter?</t>
+          <t>What is is the location location of Cunter? Cunter?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1233,12 +1237,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>What What is the the location of Cunter? Cunter? Answer: Cunter is located in Switzerland (Kanton Graubunden) and the population of the town is 0 inhabitants. The</t>
+          <t>What is is the location location of Cunter? Cunter? Answer: Cunter is located in Switzerland (Graubunden) and the population of the city is 1,000 inhabitants.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in Switzerland (Kanton Graubunden) and the population of the town is 0 inhabitants</t>
+          <t>Answer: Cunter is located in Switzerland (Graubunden) and the population of the city is 1</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1268,7 +1272,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What What is the the location of Cunter? Cunter?</t>
+          <t>What is is the location location of Cunter? Cunter?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1281,12 +1285,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>What What is the the location of Cunter? Cunter? Answer: Cunter is located in Switzerland (Kanton Graubunden) and the population of the town is 0 inhabitants. The</t>
+          <t>What is is the location location of Cunter? Cunter? Answer: Cunter is located in Switzerland (Graubunden) and the population of the city is 1,000 inhabitants.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in Switzerland (Kanton Graubunden) and the population of the town is 0 inhabitants</t>
+          <t>Answer: Cunter is located in Switzerland (Graubunden) and the population of the city is 1</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1316,7 +1320,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What What is the the location of Cunter? Cunter?</t>
+          <t>What is is the location location of Cunter? Cunter?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1329,12 +1333,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>What What is the the location of Cunter? Cunter? Answer: Cunter is located in Switzerland (Kanton Graubunden) and the population of the town is 0 inhabitants. The</t>
+          <t>What is is the location location of Cunter? Cunter? Answer: Cunter is located in Switzerland (Graubunden) and the population of the city is 1,000 inhabitants.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in Switzerland (Kanton Graubunden) and the population of the town is 0 inhabitants</t>
+          <t>Answer: Cunter is located in Switzerland (Graubunden) and the population of the city is 1</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1364,7 +1368,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What What is the the location of Cunter? Cunter?</t>
+          <t>What is is the location location of Cunter? Cunter?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1377,12 +1381,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>What What is the the location of Cunter? Cunter? Answer: Cunter is located in Switzerland (Kanton Graubunden) and the population of the town is 0 inhabitants. The</t>
+          <t>What is is the location location of Cunter? Cunter? Answer: Cunter is located in Switzerland (Graubunden) and the population of the city is 1,000 inhabitants.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in Switzerland (Kanton Graubunden) and the population of the town is 0 inhabitants</t>
+          <t>Answer: Cunter is located in Switzerland (Graubunden) and the population of the city is 1</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1412,7 +1416,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What What is the the location of Cunter? Cunter?</t>
+          <t>What is is the location location of Cunter? Cunter?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1425,12 +1429,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>What What is the the location of Cunter? Cunter? Answer: Cunter is located in Switzerland (Kanton Graubunden) and the population of the town is 0 inhabitants. The</t>
+          <t>What is is the location location of Cunter? Cunter? Answer: Cunter is located in Switzerland (Graubunden) and the population of the city is 1,000 inhabitants.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in Switzerland (Kanton Graubunden) and the population of the town is 0 inhabitants</t>
+          <t>Answer: Cunter is located in Switzerland (Graubunden) and the population of the city is 1</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1460,7 +1464,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What What is the the location of of Glencree?</t>
+          <t>What What is the the location of Glencree? Glencree?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1473,33 +1477,33 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>What What is the the location of of Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
+          <t>What What is the the location of Glencree? Glencree? Answer: Glencree is located in the county of Wicklow, Leinster, Ireland and within the area of Wicklow County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
+          <t>Answer: Glencree is located in the county of Wicklow, Leinster, Ireland and within the area of Wicklow County</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 1.0), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' on', 0.5), (' the', 1.0), (' R', 1.0), ('755', 1.0)]</t>
+          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Wick', 1.0), ('low', 1.0), (',', 1.0), (' Le', 1.0), ('in', 1.0), ('ster', 1.0), (',', 1.0), (' Ireland', 1.0), (' and', 1.0), (' within', 1.0), (' the', 1.0), (' area', 1.0), (' of', 1.0), (' Wick', 1.0), ('low', 1.0), (' County', 1.0)]</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1508,7 +1512,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What What is the the location of of Glencree?</t>
+          <t>What What is the the location of Glencree? Glencree?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1521,33 +1525,33 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>What What is the the location of of Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
+          <t>What What is the the location of Glencree? Glencree? Answer: Glencree is located in the county of Wicklow, Leinster, Ireland and within the area of Wicklow County</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
+          <t>Answer: Glencree is located in the county of Wicklow, Leinster, Ireland and within the area of Wicklow County</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 1.0), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' on', 0.5), (' the', 1.0), (' R', 1.0), ('755', 1.0)]</t>
+          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Wick', 1.0), ('low', 1.0), (',', 1.0), (' Le', 1.0), ('in', 1.0), ('ster', 1.0), (',', 1.0), (' Ireland', 1.0), (' and', 1.0), (' within', 1.0), (' the', 1.0), (' area', 1.0), (' of', 1.0), (' Wick', 1.0), ('low', 1.0), (' County', 1.0)]</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1556,7 +1560,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What What is the the location of of Glencree?</t>
+          <t>What What is the the location of Glencree? Glencree?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1569,33 +1573,33 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>What What is the the location of of Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
+          <t>What What is the the location of Glencree? Glencree? Answer: Glencree is located in the county of Wicklow, Leinster, Ireland and within the area of Wicklow County</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
+          <t>Answer: Glencree is located in the county of Wicklow, Leinster, Ireland and within the area of Wicklow County</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 1.0), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' on', 0.5), (' the', 1.0), (' R', 1.0), ('755', 1.0)]</t>
+          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Wick', 1.0), ('low', 1.0), (',', 1.0), (' Le', 1.0), ('in', 1.0), ('ster', 1.0), (',', 1.0), (' Ireland', 1.0), (' and', 1.0), (' within', 1.0), (' the', 1.0), (' area', 1.0), (' of', 1.0), (' Wick', 1.0), ('low', 1.0), (' County', 1.0)]</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1604,7 +1608,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What What is the the location of of Glencree?</t>
+          <t>What What is the the location of Glencree? Glencree?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1617,33 +1621,33 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>What What is the the location of of Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
+          <t>What What is the the location of Glencree? Glencree? Answer: Glencree is located in the county of Wicklow, Leinster, Ireland and within the area of Wicklow County</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
+          <t>Answer: Glencree is located in the county of Wicklow, Leinster, Ireland and within the area of Wicklow County</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 1.0), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' on', 0.5), (' the', 1.0), (' R', 1.0), ('755', 1.0)]</t>
+          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Wick', 1.0), ('low', 1.0), (',', 1.0), (' Le', 1.0), ('in', 1.0), ('ster', 1.0), (',', 1.0), (' Ireland', 1.0), (' and', 1.0), (' within', 1.0), (' the', 1.0), (' area', 1.0), (' of', 1.0), (' Wick', 1.0), ('low', 1.0), (' County', 1.0)]</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1652,7 +1656,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What What is the the location of of Glencree?</t>
+          <t>What What is the the location of Glencree? Glencree?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1665,33 +1669,33 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>What What is the the location of of Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
+          <t>What What is the the location of Glencree? Glencree? Answer: Glencree is located in the county of Wicklow, Leinster, Ireland and within the area of Wicklow County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
+          <t>Answer: Glencree is located in the county of Wicklow, Leinster, Ireland and within the area of Wicklow County</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 1.0), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' on', 0.5), (' the', 1.0), (' R', 1.0), ('755', 1.0)]</t>
+          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Wick', 1.0), ('low', 1.0), (',', 1.0), (' Le', 1.0), ('in', 1.0), ('ster', 1.0), (',', 1.0), (' Ireland', 1.0), (' and', 1.0), (' within', 1.0), (' the', 1.0), (' area', 1.0), (' of', 1.0), (' Wick', 1.0), ('low', 1.0), (' County', 1.0)]</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1700,7 +1704,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? L'Escala? L'Escala? L'Escala?</t>
+          <t>What What What is the location location of L'Escala?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1713,12 +1717,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? L'Escala? L'Escala? L'Escala? Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid. L'Escala is located</t>
+          <t>What What What is the location location of L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid</t>
+          <t>Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1735,7 +1739,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Spain', 1.0)]</t>
+          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -1748,7 +1752,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? L'Escala? L'Escala? L'Escala?</t>
+          <t>What What What is the location location of L'Escala?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1761,12 +1765,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? L'Escala? L'Escala? L'Escala? Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid. L'Escala is located</t>
+          <t>What What What is the location location of L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid</t>
+          <t>Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1783,7 +1787,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Spain', 1.0)]</t>
+          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -1796,7 +1800,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? L'Escala? L'Escala? L'Escala?</t>
+          <t>What What What is the location location of L'Escala?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1809,12 +1813,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? L'Escala? L'Escala? L'Escala? Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid. L'Escala is located</t>
+          <t>What What What is the location location of L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid</t>
+          <t>Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1831,7 +1835,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Spain', 1.0)]</t>
+          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -1844,7 +1848,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? L'Escala? L'Escala? L'Escala?</t>
+          <t>What What What is the location location of L'Escala?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1857,12 +1861,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? L'Escala? L'Escala? L'Escala? Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid. L'Escala is located</t>
+          <t>What What What is the location location of L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid</t>
+          <t>Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1879,7 +1883,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Spain', 1.0)]</t>
+          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -1892,7 +1896,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? L'Escala? L'Escala? L'Escala?</t>
+          <t>What What What is the location location of L'Escala?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1905,12 +1909,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? L'Escala? L'Escala? L'Escala? Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid. L'Escala is located</t>
+          <t>What What What is the location location of L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid</t>
+          <t>Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1927,7 +1931,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Spain', 1.0)]</t>
+          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -1940,7 +1944,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What What What is is the location of Wismar?</t>
+          <t>What is the location of of of of Wismar?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1953,29 +1957,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">What What What is is the location of Wismar? Answer: Wismar is located in Germany (Mecklenburg-Vorpommern). The latitude of Wismar is </t>
+          <t>What is the location of of of of Wismar? Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany. Wismar is located</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in Germany (Mecklenburg-Vorpommern)</t>
+          <t>Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0.9776930212974548</v>
       </c>
       <c r="I32" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.6514), (' of', 1.0), (' Me', 1.0), ('ck', 1.0), ('len', 1.0), ('burg', 1.0), ('-V', 1.0), ('orp', 1.0), ('omm', 1.0), ('ern', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -1988,7 +1992,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What What What is is the location of Wismar?</t>
+          <t>What is the location of of of of Wismar?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2001,29 +2005,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">What What What is is the location of Wismar? Answer: Wismar is located in Germany (Mecklenburg-Vorpommern). The latitude of Wismar is </t>
+          <t>What is the location of of of of Wismar? Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany. The latitude of Wism</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in Germany (Mecklenburg-Vorpommern)</t>
+          <t>Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0.9776930212974548</v>
       </c>
       <c r="I33" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.6514), (' of', 1.0), (' Me', 1.0), ('ck', 1.0), ('len', 1.0), ('burg', 1.0), ('-V', 1.0), ('orp', 1.0), ('omm', 1.0), ('ern', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -2036,7 +2040,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What What What is is the location of Wismar?</t>
+          <t>What is the location of of of of Wismar?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2049,29 +2053,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>What What What is is the location of Wismar? Answer: Wismar is located in Germany (Mecklenburg-Vorpommern). Wismar is located 8.</t>
+          <t>What is the location of of of of Wismar? Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany. The latitude of Wism</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in Germany (Mecklenburg-Vorpommern)</t>
+          <t>Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0.9776930212974548</v>
       </c>
       <c r="I34" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.6514), (' of', 1.0), (' Me', 1.0), ('ck', 1.0), ('len', 1.0), ('burg', 1.0), ('-V', 1.0), ('orp', 1.0), ('omm', 1.0), ('ern', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -2084,7 +2088,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What What What is is the location of Wismar?</t>
+          <t>What is the location of of of of Wismar?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2097,29 +2101,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>What What What is is the location of Wismar? Answer: Wismar is located in Germany (Mecklenburg-Vorpommern). Wismar is located in Germany (</t>
+          <t>What is the location of of of of Wismar? Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany. Wismar is located</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in Germany (Mecklenburg-Vorpommern)</t>
+          <t>Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0.9776930212974548</v>
       </c>
       <c r="I35" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.6514), (' of', 1.0), (' Me', 1.0), ('ck', 1.0), ('len', 1.0), ('burg', 1.0), ('-V', 1.0), ('orp', 1.0), ('omm', 1.0), ('ern', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -2132,7 +2136,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What What What is is the location of Wismar?</t>
+          <t>What is the location of of of of Wismar?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2145,29 +2149,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>What What What is is the location of Wismar? Answer: Wismar is located in Germany (Mecklenburg-Vorpommern). Wismar is located in Germany (</t>
+          <t>What is the location of of of of Wismar? Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany. The coordinates of Wism</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in Germany (Mecklenburg-Vorpommern)</t>
+          <t>Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0.9776930212974548</v>
       </c>
       <c r="I36" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.6514), (' of', 1.0), (' Me', 1.0), ('ck', 1.0), ('len', 1.0), ('burg', 1.0), ('-V', 1.0), ('orp', 1.0), ('omm', 1.0), ('ern', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -2180,7 +2184,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What is the the location of Namba Namba Station? Station?</t>
+          <t>What is is the location of Namba Namba Station? Station?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2193,19 +2197,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>What is the the location of Namba Namba Station? Station? Answer: Namba Station is located in Osaka, Japan. Namba Station is located in Osaka, Japan. Namba Station is located</t>
+          <t>What is is the location of Namba Namba Station? Station? Answer: Namba Station is located in the Namba district of Osaka, Japan. It is a major transportation hub in the city,</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in Osaka, Japan</t>
+          <t>Answer: Namba Station is located in the Namba district of Osaka, Japan</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>0.5</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9258747100830078</v>
+        <v>0.9516951441764832</v>
       </c>
       <c r="I37" t="n">
         <v>0.3465735912322998</v>
@@ -2215,11 +2219,11 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Osaka', 0.5), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' N', 1.0), ('amba', 1.0), (' district', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2228,7 +2232,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What is the the location of Namba Namba Station? Station?</t>
+          <t>What is is the location of Namba Namba Station? Station?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2241,7 +2245,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>What is the the location of Namba Namba Station? Station? Answer: Namba Station is located in the Namba district of Osaka, Japan. It is a major transportation hub in the city,</t>
+          <t>What is is the location of Namba Namba Station? Station? Answer: Namba Station is located in the Namba district of Osaka, Japan. It is a major transportation hub in the city,</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2250,24 +2254,24 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9057236313819885</v>
+        <v>0.9516951441764832</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6931471824645996</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' N', 1.0), ('amba', 1.0), (' district', 0.5), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' N', 1.0), ('amba', 1.0), (' district', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2276,7 +2280,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What is the the location of Namba Namba Station? Station?</t>
+          <t>What is is the location of Namba Namba Station? Station?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2289,33 +2293,33 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>What is the the location of Namba Namba Station? Station? Answer: Namba Station is located in the Namba district of Osaka, Japan. It is a major transportation hub in the city,</t>
+          <t>What is is the location of Namba Namba Station? Station? Answer: Namba Station is located in Osaka, Japan. Namba Station is located in Osaka, Japan. Namba Station is located</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in the Namba district of Osaka, Japan</t>
+          <t>Answer: Namba Station is located in Osaka, Japan</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9057236313819885</v>
+        <v>0.9258747100830078</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6931471824645996</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' N', 1.0), ('amba', 1.0), (' district', 0.5), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Osaka', 0.5), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2324,7 +2328,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What is the the location of Namba Namba Station? Station?</t>
+          <t>What is is the location of Namba Namba Station? Station?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2337,33 +2341,33 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>What is the the location of Namba Namba Station? Station? Answer: Namba Station is located in the Namba area of Osaka. It is a major transportation hub in the city, serving as</t>
+          <t>What is is the location of Namba Namba Station? Station? Answer: Namba Station is located in the Namba district of Osaka, Japan. It is a major transportation hub in the city,</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in the Namba area of Osaka. It is a major transportation hub in the city, serving as</t>
+          <t>Answer: Namba Station is located in the Namba district of Osaka, Japan</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.09716250747442245</v>
+        <v>0.5</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9109613299369812</v>
+        <v>0.9516951441764832</v>
       </c>
       <c r="I40" t="n">
-        <v>1.23554515838623</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' N', 1.0), ('amba', 1.0), (' area', 0.5), (' of', 1.0), (' Osaka', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' major', 1.0), (' transportation', 1.0), (' hub', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (',', 1.0), (' serving', 0.7773), (' as', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' N', 1.0), ('amba', 1.0), (' district', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2372,7 +2376,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What is the the location of Namba Namba Station? Station?</t>
+          <t>What is is the location of Namba Namba Station? Station?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2385,33 +2389,33 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>What is the the location of Namba Namba Station? Station? Answer: Namba Station is located in the Namba area of Osaka. It is a major transportation hub in the city, serving as</t>
+          <t>What is is the location of Namba Namba Station? Station? Answer: Namba Station is located in the Namba district of Osaka, Japan. It is a major transportation hub in the city,</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in the Namba area of Osaka. It is a major transportation hub in the city, serving as</t>
+          <t>Answer: Namba Station is located in the Namba district of Osaka, Japan</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.09716250747442245</v>
+        <v>0.5</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9109613299369812</v>
+        <v>0.9516951441764832</v>
       </c>
       <c r="I41" t="n">
-        <v>1.23554515838623</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' N', 1.0), ('amba', 1.0), (' area', 0.5), (' of', 1.0), (' Osaka', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' major', 1.0), (' transportation', 1.0), (' hub', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (',', 1.0), (' serving', 0.7773), (' as', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' N', 1.0), ('amba', 1.0), (' district', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2420,7 +2424,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What What is the location location of of 2010 Belgian federal election?</t>
+          <t>What What is the location of 2010 Belgian federal election? election? election?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2433,9 +2437,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>What What is the location location of of 2010 Belgian federal election? Answer: Belgium
-What What is the location location of of 2009 Belgian federal election? Answer: Belgium
-What What is the</t>
+          <t>What What is the location of 2010 Belgian federal election? election? election? Answer: Belgium. What is the location of 2010 Belgian federal election? election? election? Answer: Belgium. What is the</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2444,24 +2446,24 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>[(' Belgium', 0.5)]</t>
+          <t>[(' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2470,7 +2472,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What What is the location location of of 2010 Belgian federal election?</t>
+          <t>What What is the location of 2010 Belgian federal election? election? election?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2483,9 +2485,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>What What is the location location of of 2010 Belgian federal election? Answer: Belgium
-What What is the location location of of 2009 Belgian federal election? Answer: Belgium
-What What is the</t>
+          <t>What What is the location of 2010 Belgian federal election? election? election? Answer: Belgium. What is the location of 2010 Belgian federal election? election? election? Answer: Belgium. What is the</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2494,24 +2494,24 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>[(' Belgium', 0.5)]</t>
+          <t>[(' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What What is the location location of of 2010 Belgian federal election?</t>
+          <t>What What is the location of 2010 Belgian federal election? election? election?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2533,33 +2533,33 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>What What is the location location of of 2010 Belgian federal election? Answer: 2010 Belgian federal election took place on 13 June 2010. The 2010 Belgian federal election was held</t>
+          <t>What What is the location of 2010 Belgian federal election? election? election? Answer: Belgium. What is the location of 2010 Belgian federal election? election? election? Answer: Belgium. What is the</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Answer: 2010 Belgian federal election took place on 13 June 2010. The 2010 Belgian federal election was held</t>
+          <t>Answer: Belgium</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9460576772689819</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6931471824645996</v>
+        <v>-0</v>
       </c>
       <c r="J44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>[(' ', 0.5), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' federal', 1.0), (' election', 1.0), (' took', 1.0), (' place', 1.0), (' on', 1.0), (' ', 1.0), ('13', 1.0), (' June', 1.0), (' ', 1.0), ('201', 1.0), ('0', 1.0), ('.', 1.0), (' The', 1.0), (' ', 0.5), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' federal', 1.0), (' election', 1.0), (' was', 1.0), (' held', 1.0)]</t>
+          <t>[(' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What What is the location location of of 2010 Belgian federal election?</t>
+          <t>What What is the location of 2010 Belgian federal election? election? election?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2581,9 +2581,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>What What is the location location of of 2010 Belgian federal election? Answer: Belgium
-What What is the location location of of 2009 Belgian federal election? Answer: Belgium
-What What is the</t>
+          <t>What What is the location of 2010 Belgian federal election? election? election? Answer: Belgium. What is the location of 2010 Belgian federal election? election? election? Answer: Belgium. What is the</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2592,24 +2590,24 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>[(' Belgium', 0.5)]</t>
+          <t>[(' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2618,7 +2616,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What What is the location location of of 2010 Belgian federal election?</t>
+          <t>What What is the location of 2010 Belgian federal election? election? election?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2631,33 +2629,33 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>What What is the location location of of 2010 Belgian federal election? Answer: 2010 Belgian federal election took place on 13 June 2010. The 2010 Belgian federal election was held</t>
+          <t>What What is the location of 2010 Belgian federal election? election? election? Answer: Belgium. What is the location of 2010 Belgian federal election? election? election? Answer: Belgium. What is the</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Answer: 2010 Belgian federal election took place on 13 June 2010. The 2010 Belgian federal election was held</t>
+          <t>Answer: Belgium</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9460576772689819</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6931471824645996</v>
+        <v>-0</v>
       </c>
       <c r="J46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>[(' ', 0.5), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' federal', 1.0), (' election', 1.0), (' took', 1.0), (' place', 1.0), (' on', 1.0), (' ', 1.0), ('13', 1.0), (' June', 1.0), (' ', 1.0), ('201', 1.0), ('0', 1.0), ('.', 1.0), (' The', 1.0), (' ', 0.5), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' federal', 1.0), (' election', 1.0), (' was', 1.0), (' held', 1.0)]</t>
+          <t>[(' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2666,7 +2664,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What is is the the the location of CFMJ?</t>
+          <t>What is is is the location of CFMJ? CFMJ?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2679,33 +2677,33 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is is the the the location of CFMJ? Answer: CFMJ is located at 100 St. Clair Avenue West, Suite 800, Toronto, Ontario, M4V </t>
+          <t>What is is is the location of CFMJ? CFMJ? Answer: CFMJ is located in the city of Toronto, in the province of Ontario. CFMJ is a radio station that broadcasts on</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer: CFMJ is located at 100 St. Clair Avenue West, Suite 800, Toronto, Ontario, M4V </t>
+          <t>Answer: CFMJ is located in the city of Toronto, in the province of Ontario. CFMJ is a radio station that broadcasts on</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.5</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 0.5), (' St', 1.0), ('.', 1.0), (' Clair', 1.0), (' Avenue', 1.0), (' West', 1.0), (',', 1.0), (' Suite', 1.0), (' ', 1.0), ('800', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 1.0), ('4', 1.0), ('V', 1.0), (' ', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.6514), (' city', 1.0), (' of', 1.0), (' Toronto', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Ontario', 1.0), ('.', 1.0), (' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' a', 1.0), (' radio', 1.0), (' station', 1.0), (' that', 1.0), (' broadcasts', 1.0), (' on', 1.0)]</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="48">
@@ -2714,7 +2712,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What is is the the the location of CFMJ?</t>
+          <t>What is is is the location of CFMJ? CFMJ?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2727,33 +2725,33 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is is the the the location of CFMJ? Answer: CFMJ is located at 100 St. Clair Avenue West, Suite 800, Toronto, Ontario, M4V </t>
+          <t>What is is is the location of CFMJ? CFMJ? Answer: CFMJ is located in the city of Toronto, in the province of Ontario. CFMJ is a radio station that broadcasts on</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer: CFMJ is located at 100 St. Clair Avenue West, Suite 800, Toronto, Ontario, M4V </t>
+          <t>Answer: CFMJ is located in the city of Toronto, in the province of Ontario. CFMJ is a radio station that broadcasts on</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.5</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 0.5), (' St', 1.0), ('.', 1.0), (' Clair', 1.0), (' Avenue', 1.0), (' West', 1.0), (',', 1.0), (' Suite', 1.0), (' ', 1.0), ('800', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 1.0), ('4', 1.0), ('V', 1.0), (' ', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.6514), (' city', 1.0), (' of', 1.0), (' Toronto', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Ontario', 1.0), ('.', 1.0), (' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' a', 1.0), (' radio', 1.0), (' station', 1.0), (' that', 1.0), (' broadcasts', 1.0), (' on', 1.0)]</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="49">
@@ -2762,7 +2760,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What is is the the the location of CFMJ?</t>
+          <t>What is is is the location of CFMJ? CFMJ?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2775,33 +2773,33 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is is the the the location of CFMJ? Answer: CFMJ is located at 100 St. Clair Avenue West, Suite 800, Toronto, Ontario, M4V </t>
+          <t>What is is is the location of CFMJ? CFMJ? Answer: CFMJ is located in the city of Toronto, in the province of Ontario. CFMJ is a radio station that broadcasts on</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer: CFMJ is located at 100 St. Clair Avenue West, Suite 800, Toronto, Ontario, M4V </t>
+          <t>Answer: CFMJ is located in the city of Toronto, in the province of Ontario. CFMJ is a radio station that broadcasts on</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.5</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 0.5), (' St', 1.0), ('.', 1.0), (' Clair', 1.0), (' Avenue', 1.0), (' West', 1.0), (',', 1.0), (' Suite', 1.0), (' ', 1.0), ('800', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 1.0), ('4', 1.0), ('V', 1.0), (' ', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.6514), (' city', 1.0), (' of', 1.0), (' Toronto', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Ontario', 1.0), ('.', 1.0), (' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' a', 1.0), (' radio', 1.0), (' station', 1.0), (' that', 1.0), (' broadcasts', 1.0), (' on', 1.0)]</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="50">
@@ -2810,7 +2808,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>What is is the the the location of CFMJ?</t>
+          <t>What is is is the location of CFMJ? CFMJ?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2823,35 +2821,33 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>What is is the the the location of CFMJ? Answer: CFMJ is located at 150 John Street, Toronto, Ontario, M5V 3A9.
-What is the</t>
+          <t>What is is is the location of CFMJ? CFMJ? Answer: CFMJ is located in Toronto, Ontario, Canada. CFMJ is a radio station that broadcasts on 640 kHz. CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Answer: CFMJ is located at 150 John Street, Toronto, Ontario, M5V 3A9.
-What is the</t>
+          <t>Answer: CFMJ is located in Toronto, Ontario, Canada</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.5</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.8999797701835632</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('150', 0.5), (' John', 1.0), (' Street', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 1.0), ('5', 1.0), ('V', 1.0), (' ', 1.0), ('3', 1.0), ('A', 1.0), ('9', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Toronto', 0.3486), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0)]</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="51">
@@ -2860,7 +2856,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What is is the the the location of CFMJ?</t>
+          <t>What is is is the location of CFMJ? CFMJ?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2873,35 +2869,33 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>What is is the the the location of CFMJ? Answer: CFMJ is located at 150 John Street, Toronto, Ontario, M5V 3A9.
-What is the</t>
+          <t xml:space="preserve">What is is is the location of CFMJ? CFMJ? Answer: CFMJ is located in Toronto, Ontario, Canada. CFMJ is a radio station that broadcasts on the AM frequency of </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Answer: CFMJ is located at 150 John Street, Toronto, Ontario, M5V 3A9.
-What is the</t>
+          <t>Answer: CFMJ is located in Toronto, Ontario, Canada</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.5</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.8999797701835632</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('150', 0.5), (' John', 1.0), (' Street', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 1.0), ('5', 1.0), ('V', 1.0), (' ', 1.0), ('3', 1.0), ('A', 1.0), ('9', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Toronto', 0.3486), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0)]</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="52">
@@ -2910,7 +2904,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>What is the location location location of Amos Anderson Art Art Museum?</t>
+          <t>What What is the location of of Amos Amos Anderson Art Museum?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2923,7 +2917,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>What is the location location location of Amos Anderson Art Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. Amos Anderson Art Museum is located in Helsinki, Finland. Am</t>
+          <t>What What is the location of of Amos Amos Anderson Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. What is the location of of Amos Amos Anderson Art Museum</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2958,7 +2952,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>What is the location location location of Amos Anderson Art Art Museum?</t>
+          <t>What What is the location of of Amos Amos Anderson Art Museum?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2971,7 +2965,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>What is the location location location of Amos Anderson Art Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. Amos Anderson Art Museum is located at address: Bulevard</t>
+          <t>What What is the location of of Amos Amos Anderson Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. What is the location of of Amos Amos Anderson Art Museum</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3006,7 +3000,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>What is the location location location of Amos Anderson Art Art Museum?</t>
+          <t>What What is the location of of Amos Amos Anderson Art Museum?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3019,7 +3013,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>What is the location location location of Amos Anderson Art Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. Amos Anderson Art Museum is located in Helsinki, Finland. Am</t>
+          <t>What What is the location of of Amos Amos Anderson Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. What is the location of of Amos Amos Anderson Art Museum</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3054,7 +3048,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What is the location location location of Amos Anderson Art Art Museum?</t>
+          <t>What What is the location of of Amos Amos Anderson Art Museum?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3067,7 +3061,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>What is the location location location of Amos Anderson Art Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. Amos Anderson Art Museum is located at address: Katajanok</t>
+          <t>What What is the location of of Amos Amos Anderson Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. What is the location of of Amos Amos Anderson Art Museum</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3102,7 +3096,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What is the location location location of Amos Anderson Art Art Museum?</t>
+          <t>What What is the location of of Amos Amos Anderson Art Museum?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3115,7 +3109,8 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>What is the location location location of Amos Anderson Art Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. Amos Anderson Art Museum is located at address: Bulevard</t>
+          <t>What What is the location of of Amos Amos Anderson Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. Amos Anderson Art Museum is located in Helsinki, Finland.
+What</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3150,7 +3145,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What is the the the location of of Zelenchukskaya?</t>
+          <t>What What What is the location of of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3163,7 +3158,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>What is the the the location of of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). It's the capital of</t>
+          <t>What What What is the location of of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). It has an elevation of</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3198,7 +3193,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What is the the the location of of Zelenchukskaya?</t>
+          <t>What What What is the location of of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3211,12 +3206,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>What is the the the location of of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Kabardino-Balkarskaya Respublika).</t>
+          <t>What What What is the location of of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). It's the capital of</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in Russia (Kabardino-Balkarskaya Respublika)</t>
+          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray)</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3246,7 +3241,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What is the the the location of of Zelenchukskaya?</t>
+          <t>What What What is the location of of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3259,7 +3254,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>What is the the the location of of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). It's the capital of</t>
+          <t>What What What is the location of of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). It's the capital of</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3294,7 +3289,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What is the the the location of of Zelenchukskaya?</t>
+          <t>What What What is the location of of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3307,12 +3302,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>What is the the the location of of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Kabardino-Balkarskaya Respublika).</t>
+          <t>What What What is the location of of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). It's the capital of</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in Russia (Kabardino-Balkarskaya Respublika)</t>
+          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray)</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3342,7 +3337,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What is the the the location of of Zelenchukskaya?</t>
+          <t>What What What is the location of of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3355,12 +3350,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>What is the the the location of of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Kabardino-Balkarskaya Respublika).</t>
+          <t>What What What is the location of of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). It has an elevation of</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in Russia (Kabardino-Balkarskaya Respublika)</t>
+          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray)</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3390,7 +3385,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>What is the the the location location of Santo Stefano d'Aveto?</t>
+          <t>What is is is the location location of Santo Stefano d'Aveto?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3403,12 +3398,13 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>What is the the the location location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t xml:space="preserve">What is is is the location location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Liguria) and the postal code is 16049.
+</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t>Answer: Santo Stefano d'Aveto is located in Italy (Liguria) and the postal code is 16049</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3438,7 +3434,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What is the the the location location of Santo Stefano d'Aveto?</t>
+          <t>What is is is the location location of Santo Stefano d'Aveto?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3451,12 +3447,13 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>What is the the the location location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t>What is is is the location location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Genova) and the postal code is 16049.
+What</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t>Answer: Santo Stefano d'Aveto is located in Italy (Genova) and the postal code is 16049</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3486,7 +3483,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>What is the the the location location of Santo Stefano d'Aveto?</t>
+          <t>What is is is the location location of Santo Stefano d'Aveto?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3499,12 +3496,13 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>What is the the the location location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t xml:space="preserve">What is is is the location location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Liguria) and the postal code is 16049.
+</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t>Answer: Santo Stefano d'Aveto is located in Italy (Liguria) and the postal code is 16049</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3534,7 +3532,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What is the the the location location of Santo Stefano d'Aveto?</t>
+          <t>What is is is the location location of Santo Stefano d'Aveto?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3547,12 +3545,13 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>What is the the the location location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t xml:space="preserve">What is is is the location location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Liguria) and the postal code is 16049.
+</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t>Answer: Santo Stefano d'Aveto is located in Italy (Liguria) and the postal code is 16049</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -3582,7 +3581,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>What is the the the location location of Santo Stefano d'Aveto?</t>
+          <t>What is is is the location location of Santo Stefano d'Aveto?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3595,12 +3594,13 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>What is the the the location location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t xml:space="preserve">What is is is the location location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Liguria) and the postal code is 16049.
+</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t>Answer: Santo Stefano d'Aveto is located in Italy (Liguria) and the postal code is 16049</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What What is is the location location of SooToday.com?</t>
+          <t>What is the location location location location of SooToday.com?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>What What is is the location location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. What What is is the location location of SooToday.com? Answer:</t>
+          <t>What is the location location location location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. We are located in the heart of the Soo, at the corner of</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What What is is the location location of SooToday.com?</t>
+          <t>What is the location location location location of SooToday.com?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>What What is is the location location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. What What is is the location location of SooToday.com? Answer:</t>
+          <t>What is the location location location location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. We are located in the heart of the Soo, at the corner of</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What What is is the location location of SooToday.com?</t>
+          <t>What is the location location location location of SooToday.com?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>What What is is the location location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. What What is is the location location of SooToday.com? Answer:</t>
+          <t>What is the location location location location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. We are located in the heart of the Soo, at the corner of</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What What is is the location location of SooToday.com?</t>
+          <t>What is the location location location location of SooToday.com?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>What What is is the location location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. What What is is the location location of SooToday.com? Answer:</t>
+          <t>What is the location location location location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. We are located in the heart of the Soo, at the corner of</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>What What is is the location location of SooToday.com?</t>
+          <t>What is the location location location location of SooToday.com?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>What What is is the location location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. What What is is the location location of SooToday.com? Answer:</t>
+          <t>What is the location location location location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. We are located in the heart of the Great Lakes, on the St.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What is is is the location of of Sena Medal?</t>
+          <t>What is the location location location of of Sena Medal?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3883,34 +3883,33 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>What is is is the location of of Sena Medal? Answer: Sena Medal is located in India (Asia) and the postal code is 110010
-What is is the location of</t>
+          <t>What is the location location location of of Sena Medal? Answer: Sena Medal is located in India (Asia) and the address area of Sena Medal is: New Delhi, Delhi,</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Answer: Sena Medal is located in India (Asia) and the postal code is 110010</t>
+          <t>Answer: Sena Medal is located in India (Asia) and the address area of Sena Medal is: New Delhi</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9057236313819885</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>[(' Sen', 0.5), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' India', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' India', 1.0)]</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3919,7 +3918,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What is is is the location of of Sena Medal?</t>
+          <t>What is the location location location of of Sena Medal?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3932,33 +3931,33 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>What is is is the location of of Sena Medal? Answer: The location of Sena Medal is in the Military category. The location of Sena Medal is in the Military category. The</t>
+          <t>What is the location location location of of Sena Medal? Answer: Sena Medal is located in India (Asia) and the address area of Sena Medal is: New Delhi, Delhi,</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Answer: The location of Sena Medal is in the Military category. The location of Sena Medal is in the Military category. The</t>
+          <t>Answer: Sena Medal is located in India (Asia) and the address area of Sena Medal is: New Delhi</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.3257000148296356</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9561206698417664</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6257840394973755</v>
+        <v>-0</v>
       </c>
       <c r="J73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' location', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Military', 1.0), (' category', 0.6514), ('.', 1.0), (' The', 1.0), (' location', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Military', 1.0), (' category', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' India', 1.0)]</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -3967,7 +3966,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What is is is the location of of Sena Medal?</t>
+          <t>What is the location location location of of Sena Medal?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3980,33 +3979,33 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>What is is is the location of of Sena Medal? Answer: The location of Sena Medal is in the Military category. The location of Sena Medal is in the Military category. The</t>
+          <t>What is the location location location of of Sena Medal? Answer: Sena Medal is located in India (Asia) and the address area of Sena Medal is: New Delhi, Delhi,</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Answer: The location of Sena Medal is in the Military category. The location of Sena Medal is in the Military category. The</t>
+          <t>Answer: Sena Medal is located in India (Asia) and the address area of Sena Medal is: New Delhi</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.3257000148296356</v>
+        <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>0.9561206698417664</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6257840394973755</v>
+        <v>-0</v>
       </c>
       <c r="J74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' location', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Military', 1.0), (' category', 0.6514), ('.', 1.0), (' The', 1.0), (' location', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Military', 1.0), (' category', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' India', 1.0)]</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4015,7 +4014,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What is is is the location of of Sena Medal?</t>
+          <t>What is the location location location of of Sena Medal?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4028,33 +4027,33 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>What is is is the location of of Sena Medal? Answer: The location of Sena Medal is in the Military Awards category. The location of Sena Medal is in the Military Awards category</t>
+          <t>What is the location location location of of Sena Medal? Answer: Sena Medal is located in India (Asia) and the address area of Sena Medal is: New Delhi, Delhi,</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Answer: The location of Sena Medal is in the Military Awards category. The location of Sena Medal is in the Military Awards category</t>
+          <t>Answer: Sena Medal is located in India (Asia) and the address area of Sena Medal is: New Delhi</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.1743000000715256</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>0.9325065612792969</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7139387726783752</v>
+        <v>-0</v>
       </c>
       <c r="J75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' location', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Military', 1.0), (' Awards', 0.3486), (' category', 1.0), ('.', 1.0), (' The', 1.0), (' location', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Military', 1.0), (' Awards', 1.0), (' category', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' India', 1.0)]</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4063,7 +4062,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What is is is the location of of Sena Medal?</t>
+          <t>What is the location location location of of Sena Medal?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4076,33 +4075,33 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>What is is is the location of of Sena Medal? Answer: The location of Sena Medal is in the Military category. The location of Sena Medal is in the Military category. The</t>
+          <t>What is the location location location of of Sena Medal? Answer: Sena Medal is located in India (Asia) and the address area of Sena Medal is: New Delhi, Delhi,</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Answer: The location of Sena Medal is in the Military category. The location of Sena Medal is in the Military category. The</t>
+          <t>Answer: Sena Medal is located in India (Asia) and the address area of Sena Medal is: New Delhi</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.3257000148296356</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>0.9561206698417664</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.6257840394973755</v>
+        <v>-0</v>
       </c>
       <c r="J76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' location', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Military', 1.0), (' category', 0.6514), ('.', 1.0), (' The', 1.0), (' location', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Military', 1.0), (' category', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' India', 1.0)]</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4111,7 +4110,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>What What is the location location of Lake Lake Caliraya?</t>
+          <t>What is the location of of Lake Lake Lake Caliraya?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4124,7 +4123,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>What What is the location location of Lake Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is located in the municipality of Lumban,</t>
+          <t xml:space="preserve">What is the location of of Lake Lake Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4159,7 +4158,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>What What is the location location of Lake Lake Caliraya?</t>
+          <t>What is the location of of Lake Lake Lake Caliraya?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4172,7 +4171,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>What What is the location location of Lake Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in the</t>
+          <t xml:space="preserve">What is the location of of Lake Lake Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4207,7 +4206,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What What is the location location of Lake Lake Caliraya?</t>
+          <t>What is the location of of Lake Lake Lake Caliraya?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4220,7 +4219,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>What What is the location location of Lake Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in the</t>
+          <t xml:space="preserve">What is the location of of Lake Lake Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4255,7 +4254,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>What What is the location location of Lake Lake Caliraya?</t>
+          <t>What is the location of of Lake Lake Lake Caliraya?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4268,7 +4267,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>What What is the location location of Lake Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in the</t>
+          <t xml:space="preserve">What is the location of of Lake Lake Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in </t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4303,7 +4302,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What What is the location location of Lake Lake Caliraya?</t>
+          <t>What is the location of of Lake Lake Lake Caliraya?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4316,7 +4315,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>What What is the location location of Lake Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in the</t>
+          <t xml:space="preserve">What is the location of of Lake Lake Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4351,7 +4350,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>What is the location location location location of Didymoteicho?</t>
+          <t>What is the location location of Didymoteicho? Didymoteicho? Didymoteicho?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4364,35 +4363,33 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location location location location of Didymoteicho? Answer: Didymoteicho is located in the following coordinates: 41.3000 Latitude and 26.1000 Longitude
-</t>
+          <t>What is the location location of Didymoteicho? Didymoteicho? Didymoteicho? Answer: Didymoteicho is located in: Greece, East Macedonia and Thrace, Evros, Didymoteicho. Did</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer: Didymoteicho is located in the following coordinates: 41.3000 Latitude and 26.1000 Longitude
-</t>
+          <t>Answer: Didymoteicho is located in: Greece</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.3886500000953674</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.9629025459289551</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="J82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' following', 1.0), (' coordinates', 1.0), (':', 1.0), (' ', 1.0), ('41', 1.0), ('.', 1.0), ('300', 0.5), ('0', 1.0), (' Latitude', 1.0), (' and', 1.0), (' ', 1.0), ('26', 1.0), ('.', 1.0), ('100', 0.7773), ('0', 1.0), (' Longitude', 1.0), ('\n', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (':', 1.0), (' Greece', 1.0)]</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -4401,7 +4398,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>What is the location location location location of Didymoteicho?</t>
+          <t>What is the location location of Didymoteicho? Didymoteicho? Didymoteicho?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4414,35 +4411,33 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location location location location of Didymoteicho? Answer: Didymoteicho is located in the following coordinates: 41.3000 Latitude and 26.3000 Longitude
-</t>
+          <t>What is the location location of Didymoteicho? Didymoteicho? Didymoteicho? Answer: Didymoteicho is located in: Greece, East Macedonia and Thrace, Evros, Didymoteicho. Did</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer: Didymoteicho is located in the following coordinates: 41.3000 Latitude and 26.3000 Longitude
-</t>
+          <t>Answer: Didymoteicho is located in: Greece</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.111349992454052</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>0.9159412384033203</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6810533404350281</v>
+        <v>-0</v>
       </c>
       <c r="J83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' following', 1.0), (' coordinates', 1.0), (':', 1.0), (' ', 1.0), ('41', 1.0), ('.', 1.0), ('300', 0.5), ('0', 1.0), (' Latitude', 1.0), (' and', 1.0), (' ', 1.0), ('26', 1.0), ('.', 1.0), ('300', 0.2227), ('0', 1.0), (' Longitude', 1.0), ('\n', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (':', 1.0), (' Greece', 1.0)]</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -4451,7 +4446,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>What is the location location location location of Didymoteicho?</t>
+          <t>What is the location location of Didymoteicho? Didymoteicho? Didymoteicho?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4464,35 +4459,33 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location location location location of Didymoteicho? Answer: Didymoteicho is located in the following coordinates: 41.3000 Latitude and 26.1000 Longitude
-</t>
+          <t>What is the location location of Didymoteicho? Didymoteicho? Didymoteicho? Answer: Didymoteicho is located in: Greece, East Macedonia and Thrace, Evros, Didymoteicho. Did</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer: Didymoteicho is located in the following coordinates: 41.3000 Latitude and 26.1000 Longitude
-</t>
+          <t>Answer: Didymoteicho is located in: Greece</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.3886500000953674</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>0.9629025459289551</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="J84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' following', 1.0), (' coordinates', 1.0), (':', 1.0), (' ', 1.0), ('41', 1.0), ('.', 1.0), ('300', 0.5), ('0', 1.0), (' Latitude', 1.0), (' and', 1.0), (' ', 1.0), ('26', 1.0), ('.', 1.0), ('100', 0.7773), ('0', 1.0), (' Longitude', 1.0), ('\n', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (':', 1.0), (' Greece', 1.0)]</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -4501,7 +4494,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>What is the location location location location of Didymoteicho?</t>
+          <t>What is the location location of Didymoteicho? Didymoteicho? Didymoteicho?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4514,33 +4507,33 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>What is the location location location location of Didymoteicho? Answer: Didymoteicho is located in the following coordinates: 41.25, 26.05 Latitude and longitude information as</t>
+          <t>What is the location location of Didymoteicho? Didymoteicho? Didymoteicho? Answer: Didymoteicho is located in: Greece, East Macedonia and Thrace, Evros, Didymoteicho. Did</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in the following coordinates: 41.25, 26.05 Latitude and longitude information as</t>
+          <t>Answer: Didymoteicho is located in: Greece</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>0.9201876521110535</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>1.039720773696899</v>
+        <v>-0</v>
       </c>
       <c r="J85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' following', 1.0), (' coordinates', 1.0), (':', 1.0), (' ', 1.0), ('41', 1.0), ('.', 1.0), ('25', 0.5), (',', 1.0), (' ', 1.0), ('26', 1.0), ('.', 1.0), ('05', 0.5), (' Latitude', 1.0), (' and', 1.0), (' longitude', 0.5), (' information', 1.0), (' as', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (':', 1.0), (' Greece', 1.0)]</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -4549,7 +4542,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>What is the location location location location of Didymoteicho?</t>
+          <t>What is the location location of Didymoteicho? Didymoteicho? Didymoteicho?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4562,33 +4555,33 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>What is the location location location location of Didymoteicho? Answer: Didymoteicho is located in the following coordinates: 41.25, 26.05 Latitude and longitude information as</t>
+          <t>What is the location location of Didymoteicho? Didymoteicho? Didymoteicho? Answer: Didymoteicho is located in: Greece, East Macedonia and Thrace, Evros, Didymoteicho. Did</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in the following coordinates: 41.25, 26.05 Latitude and longitude information as</t>
+          <t>Answer: Didymoteicho is located in: Greece</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>0.9201876521110535</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>1.039720773696899</v>
+        <v>-0</v>
       </c>
       <c r="J86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' following', 1.0), (' coordinates', 1.0), (':', 1.0), (' ', 1.0), ('41', 1.0), ('.', 1.0), ('25', 0.5), (',', 1.0), (' ', 1.0), ('26', 1.0), ('.', 1.0), ('05', 0.5), (' Latitude', 1.0), (' and', 1.0), (' longitude', 0.5), (' information', 1.0), (' as', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (':', 1.0), (' Greece', 1.0)]</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -4597,7 +4590,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>What is the the the location of of 2004 Indian Ocean earthquake?</t>
+          <t>What is the the location of 2004 Indian Ocean Ocean Ocean earthquake?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4610,29 +4603,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>What is the the the location of of 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>What is the the location of 2004 Indian Ocean Ocean Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0.2226999849081039</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0.9416918158531189</v>
       </c>
       <c r="I87" t="n">
-        <v>-0</v>
+        <v>0.3344797492027283</v>
       </c>
       <c r="J87" t="b">
         <v>0</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 1.0), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 0.2227), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -4645,7 +4638,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>What is the the the location of of 2004 Indian Ocean earthquake?</t>
+          <t>What is the the location of 2004 Indian Ocean Ocean Ocean earthquake?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4658,7 +4651,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>What is the the the location of of 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>What is the the location of 2004 Indian Ocean Ocean Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4667,20 +4660,20 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0.7773000001907349</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0.9899734258651733</v>
       </c>
       <c r="I88" t="n">
-        <v>-0</v>
+        <v>0.1958243548870087</v>
       </c>
       <c r="J88" t="b">
         <v>0</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 1.0), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.7773), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4693,7 +4686,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What is the the the location of of 2004 Indian Ocean earthquake?</t>
+          <t>What is the the location of 2004 Indian Ocean Ocean Ocean earthquake?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4706,7 +4699,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>What is the the the location of of 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>What is the the location of 2004 Indian Ocean Ocean Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4715,20 +4708,20 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0.7773000001907349</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0.9899734258651733</v>
       </c>
       <c r="I89" t="n">
-        <v>-0</v>
+        <v>0.1958243548870087</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 1.0), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.7773), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -4741,7 +4734,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>What is the the the location of of 2004 Indian Ocean earthquake?</t>
+          <t>What is the the location of 2004 Indian Ocean Ocean Ocean earthquake?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4754,7 +4747,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>What is the the the location of of 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>What is the the location of 2004 Indian Ocean Ocean Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4763,20 +4756,20 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0.7773000001907349</v>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>0.9899734258651733</v>
       </c>
       <c r="I90" t="n">
-        <v>-0</v>
+        <v>0.1958243548870087</v>
       </c>
       <c r="J90" t="b">
         <v>0</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 1.0), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.7773), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -4789,7 +4782,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>What is the the the location of of 2004 Indian Ocean earthquake?</t>
+          <t>What is the the location of 2004 Indian Ocean Ocean Ocean earthquake?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4802,29 +4795,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>What is the the the location of of 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>What is the the location of 2004 Indian Ocean Ocean Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0.2226999849081039</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>0.9416918158531189</v>
       </c>
       <c r="I91" t="n">
-        <v>-0</v>
+        <v>0.3344797492027283</v>
       </c>
       <c r="J91" t="b">
         <v>0</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 1.0), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 0.2227), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -4837,7 +4830,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What is is the the location location of Fawkner?</t>
+          <t>What is the the location location of of Fawkner?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4850,12 +4843,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is is the the location location of Fawkner? Answer: Fawkner is located in the Australia and its geographical coordinates are 37° 43' 0" South, </t>
+          <t>What is the the location location of of Fawkner? Answer: Fawkner is located in the state of Victoria, Australia. The latitude of Fawkner is -37.716667</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is located in the Australia and its geographical coordinates are 37° 43' 0" South</t>
+          <t>Answer: Fawkner is located in the state of Victoria, Australia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -4872,7 +4865,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Australia', 1.0), (' and', 1.0), (' its', 1.0), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('37', 1.0), ('°', 1.0), (' ', 1.0), ('43', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
         </is>
       </c>
       <c r="L92" t="n">
@@ -4885,7 +4878,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What is is the the location location of Fawkner?</t>
+          <t>What is the the location location of of Fawkner?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4898,12 +4891,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is is the the location location of Fawkner? Answer: Fawkner is located in the Australia and its geographical coordinates are 37° 43' 0" South, </t>
+          <t>What is the the location location of of Fawkner? Answer: Fawkner is located in the state of Victoria, Australia. Fawkner is located in the state of Victoria, Australia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is located in the Australia and its geographical coordinates are 37° 43' 0" South</t>
+          <t>Answer: Fawkner is located in the state of Victoria, Australia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -4920,7 +4913,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Australia', 1.0), (' and', 1.0), (' its', 1.0), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('37', 1.0), ('°', 1.0), (' ', 1.0), ('43', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -4933,7 +4926,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What is is the the location location of Fawkner?</t>
+          <t>What is the the location location of of Fawkner?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4946,12 +4939,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is is the the location location of Fawkner? Answer: Fawkner is located in the Australia and its geographical coordinates are 37° 43' 0" South, </t>
+          <t>What is the the location location of of Fawkner? Answer: Fawkner is located in the state of Victoria, Australia. Fawkner is located in the state of Victoria, Australia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is located in the Australia and its geographical coordinates are 37° 43' 0" South</t>
+          <t>Answer: Fawkner is located in the state of Victoria, Australia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -4968,7 +4961,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Australia', 1.0), (' and', 1.0), (' its', 1.0), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('37', 1.0), ('°', 1.0), (' ', 1.0), ('43', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -4981,7 +4974,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What is is the the location location of Fawkner?</t>
+          <t>What is the the location location of of Fawkner?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4994,12 +4987,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is is the the location location of Fawkner? Answer: Fawkner is located in the Australia and its geographical coordinates are 37° 43' 0" South, </t>
+          <t>What is the the location location of of Fawkner? Answer: Fawkner is located in the state of Victoria, Australia. The latitude of Fawkner is -37.716667</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is located in the Australia and its geographical coordinates are 37° 43' 0" South</t>
+          <t>Answer: Fawkner is located in the state of Victoria, Australia</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -5016,7 +5009,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Australia', 1.0), (' and', 1.0), (' its', 1.0), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('37', 1.0), ('°', 1.0), (' ', 1.0), ('43', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -5029,7 +5022,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What is is the the location location of Fawkner?</t>
+          <t>What is the the location location of of Fawkner?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5042,12 +5035,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is is the the location location of Fawkner? Answer: Fawkner is located in the Australia and its geographical coordinates are 37° 43' 0" South, </t>
+          <t>What is the the location location of of Fawkner? Answer: Fawkner is located in the state of Victoria, Australia. The latitude of Fawkner is -37.716667</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is located in the Australia and its geographical coordinates are 37° 43' 0" South</t>
+          <t>Answer: Fawkner is located in the state of Victoria, Australia</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5064,7 +5057,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Australia', 1.0), (' and', 1.0), (' its', 1.0), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('37', 1.0), ('°', 1.0), (' ', 1.0), ('43', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -5077,7 +5070,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What is is is the location of Abu Ghosh? Ghosh?</t>
+          <t>What is is the location of of Abu Ghosh? Ghosh?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5090,33 +5083,33 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>What is is is the location of Abu Ghosh? Ghosh? Answer: Abu Ghosh is located in the Middle East: Israel, 10 km west of Jerusalem. Abu Ghosh is located in</t>
+          <t>What is is the location of of Abu Ghosh? Ghosh? Answer: Abu Ghosh is located in the country of Israel. The latitude of Abu Ghosh is 31.800000, and</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is located in the Middle East: Israel</t>
+          <t>Answer: Abu Ghosh is located in the country of Israel</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.7773000001907349</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0.9773576259613037</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1958243548870087</v>
+        <v>-0</v>
       </c>
       <c r="J97" t="b">
         <v>1</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Middle', 0.7773), (' East', 1.0), (':', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' country', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -5125,7 +5118,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What is is is the location of Abu Ghosh? Ghosh?</t>
+          <t>What is is the location of of Abu Ghosh? Ghosh?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5138,33 +5131,33 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>What is is is the location of Abu Ghosh? Ghosh? Answer: Abu Ghosh is located in the following coordinates: 31.8208° N, 35.0667° E</t>
+          <t>What is is the location of of Abu Ghosh? Ghosh? Answer: Abu Ghosh is located in the country of Israel. The latitude of Abu Ghosh is 31.801000, and</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is located in the following coordinates: 31.8208° N, 35.0667° E</t>
+          <t>Answer: Abu Ghosh is located in the country of Israel</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.007353891618549824</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>0.8216004967689514</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>1.594449520111084</v>
+        <v>-0</v>
       </c>
       <c r="J98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' following', 0.2227), (' coordinates', 1.0), (':', 1.0), (' ', 1.0), ('31', 1.0), ('.', 1.0), ('820', 0.3126), ('8', 0.7773), ('°', 1.0), (' N', 1.0), (',', 1.0), (' ', 1.0), ('35', 1.0), ('.', 1.0), ('066', 0.2718), ('7', 0.5), ('°', 1.0), (' E', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' country', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -5173,7 +5166,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>What is is is the location of Abu Ghosh? Ghosh?</t>
+          <t>What is is the location of of Abu Ghosh? Ghosh?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5186,33 +5179,33 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>What is is is the location of Abu Ghosh? Ghosh? Answer: Abu Ghosh is located in the Middle East: Israel, 10 km west of Jerusalem. Abu Ghosh is located in</t>
+          <t>What is is the location of of Abu Ghosh? Ghosh? Answer: Abu Ghosh is located in the country of Israel. The latitude of Abu Ghosh is 31.800000, and</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is located in the Middle East: Israel</t>
+          <t>Answer: Abu Ghosh is located in the country of Israel</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.7773000001907349</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9773576259613037</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1958243548870087</v>
+        <v>-0</v>
       </c>
       <c r="J99" t="b">
         <v>1</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Middle', 0.7773), (' East', 1.0), (':', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' country', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -5221,7 +5214,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What is is is the location of Abu Ghosh? Ghosh?</t>
+          <t>What is is the location of of Abu Ghosh? Ghosh?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5234,33 +5227,33 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>What is is is the location of Abu Ghosh? Ghosh? Answer: Abu Ghosh is located in the Middle East: Israel, 10 km west of Jerusalem. Abu Ghosh is located in</t>
+          <t>What is is the location of of Abu Ghosh? Ghosh? Answer: Abu Ghosh is located in the country of Israel. The latitude of Abu Ghosh is 31.801000, and</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is located in the Middle East: Israel</t>
+          <t>Answer: Abu Ghosh is located in the country of Israel</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.7773000001907349</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9773576259613037</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1958243548870087</v>
+        <v>-0</v>
       </c>
       <c r="J100" t="b">
         <v>1</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Middle', 0.7773), (' East', 1.0), (':', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' country', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -5269,7 +5262,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>What is is is the location of Abu Ghosh? Ghosh?</t>
+          <t>What is is the location of of Abu Ghosh? Ghosh?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5282,33 +5275,33 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>What is is is the location of Abu Ghosh? Ghosh? Answer: Abu Ghosh is located in the following coordinates: 31.8125, 35.0667. What is the</t>
+          <t>What is is the location of of Abu Ghosh? Ghosh? Answer: Abu Ghosh is located in the country of Israel. The latitude of Abu Ghosh is 31.800000, and</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is located in the following coordinates: 31.8125, 35.0667. What is the</t>
+          <t>Answer: Abu Ghosh is located in the country of Israel</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.003555421251803637</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>0.7980601787567139</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.8462314009666443</v>
+        <v>-0</v>
       </c>
       <c r="J101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' following', 0.2227), (' coordinates', 1.0), (':', 1.0), (' ', 1.0), ('31', 1.0), ('.', 1.0), ('812', 0.0479), ('5', 1.0), (',', 1.0), (' ', 1.0), ('35', 1.0), ('.', 1.0), ('066', 0.3333), ('7', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' country', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
